--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2443-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2443-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{49F9AA71-8575-4D4A-945B-A5428C23BEC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{73F2286D-D786-45C3-8AD5-9A2937EFBF5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{42F4A0A5-23A6-4CC3-8156-1527354EE94D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" xr2:uid="{1610C540-A757-47F3-91C8-C0BD0FE44C13}"/>
   </bookViews>
   <sheets>
     <sheet name="2443-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="31">
   <si>
     <t>股利</t>
   </si>
@@ -37,7 +37,7 @@
     <t>股利政策</t>
   </si>
   <si>
-    <t>現金殖利率</t>
+    <t>現金+股票殖利率</t>
   </si>
   <si>
     <t>股東股利 (元/股)</t>
@@ -70,7 +70,7 @@
     <t>年度</t>
   </si>
   <si>
-    <t>除息前</t>
+    <t>除權/息前</t>
   </si>
   <si>
     <t>年均價</t>
@@ -91,10 +91,16 @@
     <t>公積</t>
   </si>
   <si>
-    <t>價格</t>
+    <t>除息</t>
+  </si>
+  <si>
+    <t>除權</t>
   </si>
   <si>
     <t>利率</t>
+  </si>
+  <si>
+    <t>價格</t>
   </si>
   <si>
     <t> 無 </t>
@@ -1406,21 +1412,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C64D1A6-2CE5-47D6-B143-B187869713F6}">
-  <dimension ref="A1:W32"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DD08B43-C646-49B2-B747-D7909BAE4B17}">
+  <dimension ref="A1:X32"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.5" customWidth="1"/>
-    <col min="3" max="3" width="10.375" customWidth="1"/>
-    <col min="4" max="17" width="6.375" customWidth="1"/>
-    <col min="18" max="18" width="6.625" customWidth="1"/>
-    <col min="19" max="19" width="6.375" customWidth="1"/>
-    <col min="20" max="20" width="6.625" customWidth="1"/>
-    <col min="21" max="22" width="6.375" customWidth="1"/>
-    <col min="23" max="23" width="7.625" customWidth="1"/>
+    <col min="1" max="2" width="12.6640625" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="14" width="7.88671875" customWidth="1"/>
+    <col min="15" max="15" width="8.21875" customWidth="1"/>
+    <col min="16" max="18" width="7.88671875" customWidth="1"/>
+    <col min="19" max="19" width="8.21875" customWidth="1"/>
+    <col min="20" max="20" width="7.88671875" customWidth="1"/>
+    <col min="21" max="21" width="8.21875" customWidth="1"/>
+    <col min="22" max="23" width="7.88671875" customWidth="1"/>
+    <col min="24" max="24" width="9.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1451,9 +1459,10 @@
       <c r="T1" s="26"/>
       <c r="U1" s="26"/>
       <c r="V1" s="26"/>
-      <c r="W1" s="18"/>
+      <c r="W1" s="26"/>
+      <c r="X1" s="18"/>
     </row>
-    <row r="2" spans="1:23" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
@@ -1486,9 +1495,10 @@
       <c r="T2" s="28"/>
       <c r="U2" s="28"/>
       <c r="V2" s="28"/>
-      <c r="W2" s="29"/>
+      <c r="W2" s="28"/>
+      <c r="X2" s="29"/>
     </row>
-    <row r="3" spans="1:23" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
         <v>2</v>
       </c>
@@ -1521,25 +1531,26 @@
       <c r="N3" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O3" s="32"/>
-      <c r="P3" s="30" t="s">
+      <c r="O3" s="31"/>
+      <c r="P3" s="32"/>
+      <c r="Q3" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="Q3" s="32"/>
-      <c r="R3" s="30" t="s">
+      <c r="R3" s="32"/>
+      <c r="S3" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="S3" s="32"/>
-      <c r="T3" s="30" t="s">
+      <c r="T3" s="32"/>
+      <c r="U3" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="U3" s="32"/>
-      <c r="V3" s="30" t="s">
+      <c r="V3" s="32"/>
+      <c r="W3" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="W3" s="32"/>
+      <c r="X3" s="32"/>
     </row>
-    <row r="4" spans="1:23" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="21"/>
       <c r="B4" s="22"/>
       <c r="C4" s="7"/>
@@ -1580,37 +1591,40 @@
         <v>24</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="S4" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="T4" s="8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="U4" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="V4" s="8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="W4" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="X4" s="8" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:23" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="33">
         <v>2022</v>
       </c>
       <c r="B5" s="34"/>
       <c r="C5" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D5" s="10">
         <v>0</v>
@@ -1634,52 +1648,55 @@
         <v>0</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L5" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M5" s="11">
         <v>2023</v>
       </c>
       <c r="N5" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="O5" s="10">
-        <v>0</v>
-      </c>
-      <c r="P5" s="12">
+        <v>28</v>
+      </c>
+      <c r="O5" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P5" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="12">
         <v>3.23</v>
       </c>
-      <c r="Q5" s="10">
-        <v>0</v>
-      </c>
-      <c r="R5" s="12">
+      <c r="R5" s="10">
+        <v>0</v>
+      </c>
+      <c r="S5" s="12">
         <v>4.22</v>
       </c>
-      <c r="S5" s="10">
-        <v>0</v>
-      </c>
-      <c r="T5" s="12">
+      <c r="T5" s="10">
+        <v>0</v>
+      </c>
+      <c r="U5" s="12">
         <v>5.4</v>
       </c>
-      <c r="U5" s="10">
-        <v>0</v>
-      </c>
-      <c r="V5" s="12">
+      <c r="V5" s="10">
+        <v>0</v>
+      </c>
+      <c r="W5" s="12">
         <v>2.27</v>
       </c>
-      <c r="W5" s="10">
+      <c r="X5" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="35">
         <v>2021</v>
       </c>
       <c r="B6" s="36"/>
       <c r="C6" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D6" s="14">
         <v>0</v>
@@ -1703,52 +1720,55 @@
         <v>0</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M6" s="15">
         <v>2022</v>
       </c>
       <c r="N6" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="O6" s="14">
-        <v>0</v>
-      </c>
-      <c r="P6" s="16">
+        <v>28</v>
+      </c>
+      <c r="O6" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="P6" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="16">
         <v>3.28</v>
       </c>
-      <c r="Q6" s="14">
-        <v>0</v>
-      </c>
-      <c r="R6" s="16">
+      <c r="R6" s="14">
+        <v>0</v>
+      </c>
+      <c r="S6" s="16">
         <v>2.81</v>
       </c>
-      <c r="S6" s="14">
-        <v>0</v>
-      </c>
-      <c r="T6" s="16">
+      <c r="T6" s="14">
+        <v>0</v>
+      </c>
+      <c r="U6" s="16">
         <v>4.9800000000000004</v>
       </c>
-      <c r="U6" s="14">
-        <v>0</v>
-      </c>
-      <c r="V6" s="16">
+      <c r="V6" s="14">
+        <v>0</v>
+      </c>
+      <c r="W6" s="16">
         <v>2.41</v>
       </c>
-      <c r="W6" s="14">
+      <c r="X6" s="14">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:23" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="33">
         <v>2020</v>
       </c>
       <c r="B7" s="34"/>
       <c r="C7" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D7" s="10">
         <v>0</v>
@@ -1772,52 +1792,55 @@
         <v>0</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M7" s="11">
         <v>2021</v>
       </c>
       <c r="N7" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="O7" s="10">
-        <v>0</v>
-      </c>
-      <c r="P7" s="12">
+        <v>28</v>
+      </c>
+      <c r="O7" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P7" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="12">
         <v>2.89</v>
       </c>
-      <c r="Q7" s="10">
-        <v>0</v>
-      </c>
-      <c r="R7" s="12">
+      <c r="R7" s="10">
+        <v>0</v>
+      </c>
+      <c r="S7" s="12">
         <v>3.41</v>
       </c>
-      <c r="S7" s="10">
-        <v>0</v>
-      </c>
-      <c r="T7" s="12">
+      <c r="T7" s="10">
+        <v>0</v>
+      </c>
+      <c r="U7" s="12">
         <v>3.68</v>
       </c>
-      <c r="U7" s="10">
-        <v>0</v>
-      </c>
-      <c r="V7" s="12">
+      <c r="V7" s="10">
+        <v>0</v>
+      </c>
+      <c r="W7" s="12">
         <v>1.89</v>
       </c>
-      <c r="W7" s="10">
+      <c r="X7" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:23" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="35">
         <v>2019</v>
       </c>
       <c r="B8" s="36"/>
       <c r="C8" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D8" s="14">
         <v>0</v>
@@ -1841,52 +1864,55 @@
         <v>0</v>
       </c>
       <c r="K8" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L8" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M8" s="15">
         <v>2020</v>
       </c>
       <c r="N8" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="O8" s="14">
-        <v>0</v>
-      </c>
-      <c r="P8" s="16">
+        <v>28</v>
+      </c>
+      <c r="O8" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="P8" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="16">
         <v>3.64</v>
       </c>
-      <c r="Q8" s="14">
-        <v>0</v>
-      </c>
-      <c r="R8" s="16">
+      <c r="R8" s="14">
+        <v>0</v>
+      </c>
+      <c r="S8" s="16">
         <v>3.04</v>
       </c>
-      <c r="S8" s="14">
-        <v>0</v>
-      </c>
-      <c r="T8" s="16">
+      <c r="T8" s="14">
+        <v>0</v>
+      </c>
+      <c r="U8" s="16">
         <v>6.51</v>
       </c>
-      <c r="U8" s="14">
-        <v>0</v>
-      </c>
-      <c r="V8" s="16">
+      <c r="V8" s="14">
+        <v>0</v>
+      </c>
+      <c r="W8" s="16">
         <v>2.35</v>
       </c>
-      <c r="W8" s="14">
+      <c r="X8" s="14">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:23" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="33">
         <v>2018</v>
       </c>
       <c r="B9" s="34"/>
       <c r="C9" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D9" s="10">
         <v>0</v>
@@ -1910,52 +1936,55 @@
         <v>0</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M9" s="11">
         <v>2019</v>
       </c>
       <c r="N9" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="O9" s="10">
-        <v>0</v>
-      </c>
-      <c r="P9" s="12">
+        <v>28</v>
+      </c>
+      <c r="O9" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P9" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="12">
         <v>3.44</v>
       </c>
-      <c r="Q9" s="10">
-        <v>0</v>
-      </c>
-      <c r="R9" s="12">
+      <c r="R9" s="10">
+        <v>0</v>
+      </c>
+      <c r="S9" s="12">
         <v>4.12</v>
       </c>
-      <c r="S9" s="10">
-        <v>0</v>
-      </c>
-      <c r="T9" s="12">
+      <c r="T9" s="10">
+        <v>0</v>
+      </c>
+      <c r="U9" s="12">
         <v>4.5999999999999996</v>
       </c>
-      <c r="U9" s="10">
-        <v>0</v>
-      </c>
-      <c r="V9" s="12">
+      <c r="V9" s="10">
+        <v>0</v>
+      </c>
+      <c r="W9" s="12">
         <v>2.48</v>
       </c>
-      <c r="W9" s="10">
+      <c r="X9" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:23" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>2017</v>
       </c>
       <c r="B10" s="36"/>
       <c r="C10" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D10" s="14">
         <v>0</v>
@@ -1979,52 +2008,55 @@
         <v>0</v>
       </c>
       <c r="K10" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L10" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M10" s="15">
         <v>2018</v>
       </c>
       <c r="N10" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="O10" s="14">
-        <v>0</v>
-      </c>
-      <c r="P10" s="16">
+        <v>28</v>
+      </c>
+      <c r="O10" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="P10" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="16">
         <v>5.93</v>
       </c>
-      <c r="Q10" s="14">
-        <v>0</v>
-      </c>
-      <c r="R10" s="16">
+      <c r="R10" s="14">
+        <v>0</v>
+      </c>
+      <c r="S10" s="16">
         <v>4.4800000000000004</v>
       </c>
-      <c r="S10" s="14">
-        <v>0</v>
-      </c>
-      <c r="T10" s="16">
+      <c r="T10" s="14">
+        <v>0</v>
+      </c>
+      <c r="U10" s="16">
         <v>8.5399999999999991</v>
       </c>
-      <c r="U10" s="14">
-        <v>0</v>
-      </c>
-      <c r="V10" s="16">
+      <c r="V10" s="14">
+        <v>0</v>
+      </c>
+      <c r="W10" s="16">
         <v>4.45</v>
       </c>
-      <c r="W10" s="14">
+      <c r="X10" s="14">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:23" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="33">
         <v>2016</v>
       </c>
       <c r="B11" s="34"/>
       <c r="C11" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D11" s="10">
         <v>0</v>
@@ -2048,52 +2080,55 @@
         <v>0</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M11" s="11">
         <v>2017</v>
       </c>
       <c r="N11" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="O11" s="10">
-        <v>0</v>
-      </c>
-      <c r="P11" s="12">
+        <v>28</v>
+      </c>
+      <c r="O11" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P11" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="12">
         <v>6.69</v>
       </c>
-      <c r="Q11" s="10">
-        <v>0</v>
-      </c>
-      <c r="R11" s="12">
+      <c r="R11" s="10">
+        <v>0</v>
+      </c>
+      <c r="S11" s="12">
         <v>6.2</v>
       </c>
-      <c r="S11" s="10">
-        <v>0</v>
-      </c>
-      <c r="T11" s="12">
+      <c r="T11" s="10">
+        <v>0</v>
+      </c>
+      <c r="U11" s="12">
         <v>8.25</v>
       </c>
-      <c r="U11" s="10">
-        <v>0</v>
-      </c>
-      <c r="V11" s="12">
+      <c r="V11" s="10">
+        <v>0</v>
+      </c>
+      <c r="W11" s="12">
         <v>5.88</v>
       </c>
-      <c r="W11" s="10">
+      <c r="X11" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:23" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="35">
         <v>2015</v>
       </c>
       <c r="B12" s="36"/>
       <c r="C12" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D12" s="14">
         <v>0</v>
@@ -2117,52 +2152,55 @@
         <v>0</v>
       </c>
       <c r="K12" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L12" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M12" s="15">
         <v>2016</v>
       </c>
       <c r="N12" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="O12" s="14">
-        <v>0</v>
-      </c>
-      <c r="P12" s="16">
+        <v>28</v>
+      </c>
+      <c r="O12" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="P12" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="16">
         <v>7.26</v>
       </c>
-      <c r="Q12" s="14">
-        <v>0</v>
-      </c>
-      <c r="R12" s="16">
+      <c r="R12" s="14">
+        <v>0</v>
+      </c>
+      <c r="S12" s="16">
         <v>6.17</v>
       </c>
-      <c r="S12" s="14">
-        <v>0</v>
-      </c>
-      <c r="T12" s="16">
+      <c r="T12" s="14">
+        <v>0</v>
+      </c>
+      <c r="U12" s="16">
         <v>9.2799999999999994</v>
       </c>
-      <c r="U12" s="14">
-        <v>0</v>
-      </c>
-      <c r="V12" s="16">
+      <c r="V12" s="14">
+        <v>0</v>
+      </c>
+      <c r="W12" s="16">
         <v>5.8</v>
       </c>
-      <c r="W12" s="14">
+      <c r="X12" s="14">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:23" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="33">
         <v>2014</v>
       </c>
       <c r="B13" s="34"/>
       <c r="C13" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D13" s="10">
         <v>0</v>
@@ -2186,52 +2224,55 @@
         <v>0</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M13" s="11">
         <v>2015</v>
       </c>
       <c r="N13" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="O13" s="10">
-        <v>0</v>
-      </c>
-      <c r="P13" s="12">
+        <v>28</v>
+      </c>
+      <c r="O13" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P13" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="12">
         <v>10.5</v>
       </c>
-      <c r="Q13" s="10">
-        <v>0</v>
-      </c>
-      <c r="R13" s="12">
+      <c r="R13" s="10">
+        <v>0</v>
+      </c>
+      <c r="S13" s="12">
         <v>7.05</v>
       </c>
-      <c r="S13" s="10">
-        <v>0</v>
-      </c>
-      <c r="T13" s="12">
+      <c r="T13" s="10">
+        <v>0</v>
+      </c>
+      <c r="U13" s="12">
         <v>15.6</v>
       </c>
-      <c r="U13" s="10">
-        <v>0</v>
-      </c>
-      <c r="V13" s="12">
+      <c r="V13" s="10">
+        <v>0</v>
+      </c>
+      <c r="W13" s="12">
         <v>4.76</v>
       </c>
-      <c r="W13" s="10">
+      <c r="X13" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:23" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="35">
         <v>2013</v>
       </c>
       <c r="B14" s="36"/>
       <c r="C14" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D14" s="14">
         <v>0</v>
@@ -2255,52 +2296,55 @@
         <v>0</v>
       </c>
       <c r="K14" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L14" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M14" s="15">
         <v>2014</v>
       </c>
       <c r="N14" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="O14" s="14">
-        <v>0</v>
-      </c>
-      <c r="P14" s="16">
+        <v>28</v>
+      </c>
+      <c r="O14" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="P14" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="16">
         <v>10.4</v>
       </c>
-      <c r="Q14" s="14">
-        <v>0</v>
-      </c>
-      <c r="R14" s="16">
+      <c r="R14" s="14">
+        <v>0</v>
+      </c>
+      <c r="S14" s="16">
         <v>10.35</v>
       </c>
-      <c r="S14" s="14">
-        <v>0</v>
-      </c>
-      <c r="T14" s="16">
+      <c r="T14" s="14">
+        <v>0</v>
+      </c>
+      <c r="U14" s="16">
         <v>14.1</v>
       </c>
-      <c r="U14" s="14">
-        <v>0</v>
-      </c>
-      <c r="V14" s="16">
+      <c r="V14" s="14">
+        <v>0</v>
+      </c>
+      <c r="W14" s="16">
         <v>6.57</v>
       </c>
-      <c r="W14" s="14">
+      <c r="X14" s="14">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:23" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="33">
         <v>2012</v>
       </c>
       <c r="B15" s="34"/>
       <c r="C15" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D15" s="10">
         <v>0</v>
@@ -2324,52 +2368,55 @@
         <v>0</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M15" s="11">
         <v>2013</v>
       </c>
       <c r="N15" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="O15" s="10">
-        <v>0</v>
-      </c>
-      <c r="P15" s="12">
+        <v>28</v>
+      </c>
+      <c r="O15" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P15" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="12">
         <v>2.96</v>
       </c>
-      <c r="Q15" s="10">
-        <v>0</v>
-      </c>
-      <c r="R15" s="12">
+      <c r="R15" s="10">
+        <v>0</v>
+      </c>
+      <c r="S15" s="12">
         <v>7.49</v>
       </c>
-      <c r="S15" s="10">
-        <v>0</v>
-      </c>
-      <c r="T15" s="12">
+      <c r="T15" s="10">
+        <v>0</v>
+      </c>
+      <c r="U15" s="12">
         <v>8</v>
       </c>
-      <c r="U15" s="10">
-        <v>0</v>
-      </c>
-      <c r="V15" s="12">
+      <c r="V15" s="10">
+        <v>0</v>
+      </c>
+      <c r="W15" s="12">
         <v>1.24</v>
       </c>
-      <c r="W15" s="10">
+      <c r="X15" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:23" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="35">
         <v>2011</v>
       </c>
       <c r="B16" s="36"/>
       <c r="C16" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D16" s="14">
         <v>0</v>
@@ -2393,52 +2440,55 @@
         <v>0</v>
       </c>
       <c r="K16" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L16" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M16" s="15">
         <v>2012</v>
       </c>
       <c r="N16" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="O16" s="14">
-        <v>0</v>
-      </c>
-      <c r="P16" s="16">
+        <v>28</v>
+      </c>
+      <c r="O16" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="P16" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="16">
         <v>2.33</v>
       </c>
-      <c r="Q16" s="14">
-        <v>0</v>
-      </c>
-      <c r="R16" s="16">
+      <c r="R16" s="14">
+        <v>0</v>
+      </c>
+      <c r="S16" s="16">
         <v>2.38</v>
       </c>
-      <c r="S16" s="14">
-        <v>0</v>
-      </c>
-      <c r="T16" s="16">
+      <c r="T16" s="14">
+        <v>0</v>
+      </c>
+      <c r="U16" s="16">
         <v>3.48</v>
       </c>
-      <c r="U16" s="14">
-        <v>0</v>
-      </c>
-      <c r="V16" s="16">
+      <c r="V16" s="14">
+        <v>0</v>
+      </c>
+      <c r="W16" s="16">
         <v>1.71</v>
       </c>
-      <c r="W16" s="14">
+      <c r="X16" s="14">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:23" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="33">
         <v>2010</v>
       </c>
       <c r="B17" s="34"/>
       <c r="C17" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D17" s="10">
         <v>0</v>
@@ -2462,52 +2512,55 @@
         <v>0</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M17" s="11">
         <v>2011</v>
       </c>
       <c r="N17" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="O17" s="10">
-        <v>0</v>
-      </c>
-      <c r="P17" s="12">
+        <v>28</v>
+      </c>
+      <c r="O17" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P17" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="12">
         <v>3.34</v>
       </c>
-      <c r="Q17" s="10">
-        <v>0</v>
-      </c>
-      <c r="R17" s="12">
+      <c r="R17" s="10">
+        <v>0</v>
+      </c>
+      <c r="S17" s="12">
         <v>2.64</v>
       </c>
-      <c r="S17" s="10">
-        <v>0</v>
-      </c>
-      <c r="T17" s="12">
+      <c r="T17" s="10">
+        <v>0</v>
+      </c>
+      <c r="U17" s="12">
         <v>5.4</v>
       </c>
-      <c r="U17" s="10">
-        <v>0</v>
-      </c>
-      <c r="V17" s="12">
+      <c r="V17" s="10">
+        <v>0</v>
+      </c>
+      <c r="W17" s="12">
         <v>2.17</v>
       </c>
-      <c r="W17" s="10">
+      <c r="X17" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:23" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="35">
         <v>2009</v>
       </c>
       <c r="B18" s="36"/>
       <c r="C18" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D18" s="14">
         <v>0</v>
@@ -2531,52 +2584,55 @@
         <v>0</v>
       </c>
       <c r="K18" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L18" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M18" s="15">
         <v>2010</v>
       </c>
       <c r="N18" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="O18" s="14">
-        <v>0</v>
-      </c>
-      <c r="P18" s="16">
+        <v>28</v>
+      </c>
+      <c r="O18" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="P18" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="16">
         <v>6.74</v>
       </c>
-      <c r="Q18" s="14">
-        <v>0</v>
-      </c>
-      <c r="R18" s="16">
+      <c r="R18" s="14">
+        <v>0</v>
+      </c>
+      <c r="S18" s="16">
         <v>5.28</v>
       </c>
-      <c r="S18" s="14">
-        <v>0</v>
-      </c>
-      <c r="T18" s="16">
+      <c r="T18" s="14">
+        <v>0</v>
+      </c>
+      <c r="U18" s="16">
         <v>10.3</v>
       </c>
-      <c r="U18" s="14">
-        <v>0</v>
-      </c>
-      <c r="V18" s="16">
+      <c r="V18" s="14">
+        <v>0</v>
+      </c>
+      <c r="W18" s="16">
         <v>4.95</v>
       </c>
-      <c r="W18" s="14">
+      <c r="X18" s="14">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:23" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="33">
         <v>2008</v>
       </c>
       <c r="B19" s="34"/>
       <c r="C19" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D19" s="10">
         <v>0</v>
@@ -2600,52 +2656,55 @@
         <v>0</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M19" s="11">
         <v>2009</v>
       </c>
       <c r="N19" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="O19" s="10">
-        <v>0</v>
-      </c>
-      <c r="P19" s="12">
+        <v>28</v>
+      </c>
+      <c r="O19" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P19" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="12">
         <v>4.24</v>
       </c>
-      <c r="Q19" s="10">
-        <v>0</v>
-      </c>
-      <c r="R19" s="12">
+      <c r="R19" s="10">
+        <v>0</v>
+      </c>
+      <c r="S19" s="12">
         <v>8.23</v>
       </c>
-      <c r="S19" s="10">
-        <v>0</v>
-      </c>
-      <c r="T19" s="12">
+      <c r="T19" s="10">
+        <v>0</v>
+      </c>
+      <c r="U19" s="12">
         <v>8.41</v>
       </c>
-      <c r="U19" s="10">
-        <v>0</v>
-      </c>
-      <c r="V19" s="12">
+      <c r="V19" s="10">
+        <v>0</v>
+      </c>
+      <c r="W19" s="12">
         <v>1.7</v>
       </c>
-      <c r="W19" s="10">
+      <c r="X19" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:23" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="35">
         <v>2007</v>
       </c>
       <c r="B20" s="36"/>
       <c r="C20" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D20" s="14">
         <v>0</v>
@@ -2669,52 +2728,55 @@
         <v>0</v>
       </c>
       <c r="K20" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L20" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M20" s="15">
         <v>2008</v>
       </c>
       <c r="N20" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="O20" s="14">
-        <v>0</v>
-      </c>
-      <c r="P20" s="16">
+        <v>28</v>
+      </c>
+      <c r="O20" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="P20" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="16">
         <v>4.72</v>
       </c>
-      <c r="Q20" s="14">
-        <v>0</v>
-      </c>
-      <c r="R20" s="16">
+      <c r="R20" s="14">
+        <v>0</v>
+      </c>
+      <c r="S20" s="16">
         <v>1.93</v>
       </c>
-      <c r="S20" s="14">
-        <v>0</v>
-      </c>
-      <c r="T20" s="16">
+      <c r="T20" s="14">
+        <v>0</v>
+      </c>
+      <c r="U20" s="16">
         <v>9.2799999999999994</v>
       </c>
-      <c r="U20" s="14">
-        <v>0</v>
-      </c>
-      <c r="V20" s="16">
+      <c r="V20" s="14">
+        <v>0</v>
+      </c>
+      <c r="W20" s="16">
         <v>1.6</v>
       </c>
-      <c r="W20" s="14">
+      <c r="X20" s="14">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:23" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="33">
         <v>2006</v>
       </c>
       <c r="B21" s="34"/>
       <c r="C21" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D21" s="10">
         <v>0</v>
@@ -2738,52 +2800,55 @@
         <v>0</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L21" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M21" s="11">
         <v>2007</v>
       </c>
       <c r="N21" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="O21" s="10">
-        <v>0</v>
-      </c>
-      <c r="P21" s="12">
+        <v>28</v>
+      </c>
+      <c r="O21" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P21" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="12">
         <v>9.86</v>
       </c>
-      <c r="Q21" s="10">
-        <v>0</v>
-      </c>
-      <c r="R21" s="12">
+      <c r="R21" s="10">
+        <v>0</v>
+      </c>
+      <c r="S21" s="12">
         <v>9.15</v>
       </c>
-      <c r="S21" s="10">
-        <v>0</v>
-      </c>
-      <c r="T21" s="12">
+      <c r="T21" s="10">
+        <v>0</v>
+      </c>
+      <c r="U21" s="12">
         <v>14.55</v>
       </c>
-      <c r="U21" s="10">
-        <v>0</v>
-      </c>
-      <c r="V21" s="12">
+      <c r="V21" s="10">
+        <v>0</v>
+      </c>
+      <c r="W21" s="12">
         <v>5.7</v>
       </c>
-      <c r="W21" s="10">
+      <c r="X21" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:23" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="35">
         <v>2005</v>
       </c>
       <c r="B22" s="36"/>
       <c r="C22" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D22" s="14">
         <v>0</v>
@@ -2807,52 +2872,55 @@
         <v>0</v>
       </c>
       <c r="K22" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L22" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M22" s="15">
         <v>2006</v>
       </c>
       <c r="N22" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="O22" s="14">
-        <v>0</v>
-      </c>
-      <c r="P22" s="16">
+        <v>28</v>
+      </c>
+      <c r="O22" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="P22" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="16">
         <v>4.6399999999999997</v>
       </c>
-      <c r="Q22" s="14">
-        <v>0</v>
-      </c>
-      <c r="R22" s="16">
+      <c r="R22" s="14">
+        <v>0</v>
+      </c>
+      <c r="S22" s="16">
         <v>7.07</v>
       </c>
-      <c r="S22" s="14">
-        <v>0</v>
-      </c>
-      <c r="T22" s="16">
+      <c r="T22" s="14">
+        <v>0</v>
+      </c>
+      <c r="U22" s="16">
         <v>8.19</v>
       </c>
-      <c r="U22" s="14">
-        <v>0</v>
-      </c>
-      <c r="V22" s="16">
+      <c r="V22" s="14">
+        <v>0</v>
+      </c>
+      <c r="W22" s="16">
         <v>2.79</v>
       </c>
-      <c r="W22" s="14">
+      <c r="X22" s="14">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:23" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="33">
         <v>2004</v>
       </c>
       <c r="B23" s="34"/>
       <c r="C23" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D23" s="10">
         <v>0</v>
@@ -2876,52 +2944,55 @@
         <v>0</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L23" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M23" s="11">
         <v>2005</v>
       </c>
       <c r="N23" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="O23" s="10">
-        <v>0</v>
-      </c>
-      <c r="P23" s="12">
+        <v>28</v>
+      </c>
+      <c r="O23" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P23" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="12">
         <v>4.87</v>
       </c>
-      <c r="Q23" s="10">
-        <v>0</v>
-      </c>
-      <c r="R23" s="12">
+      <c r="R23" s="10">
+        <v>0</v>
+      </c>
+      <c r="S23" s="12">
         <v>4.37</v>
       </c>
-      <c r="S23" s="10">
-        <v>0</v>
-      </c>
-      <c r="T23" s="12">
+      <c r="T23" s="10">
+        <v>0</v>
+      </c>
+      <c r="U23" s="12">
         <v>7.28</v>
       </c>
-      <c r="U23" s="10">
-        <v>0</v>
-      </c>
-      <c r="V23" s="12">
+      <c r="V23" s="10">
+        <v>0</v>
+      </c>
+      <c r="W23" s="12">
         <v>2.76</v>
       </c>
-      <c r="W23" s="10">
+      <c r="X23" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:23" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="35">
         <v>2003</v>
       </c>
       <c r="B24" s="36"/>
       <c r="C24" s="15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D24" s="14">
         <v>0</v>
@@ -2945,7 +3016,7 @@
         <v>0.6</v>
       </c>
       <c r="K24" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L24" s="14">
         <v>1</v>
@@ -2954,43 +3025,46 @@
         <v>2004</v>
       </c>
       <c r="N24" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="O24" s="14">
-        <v>0</v>
-      </c>
-      <c r="P24" s="16">
+        <v>28</v>
+      </c>
+      <c r="O24" s="16">
+        <v>7.75</v>
+      </c>
+      <c r="P24" s="14">
+        <v>7.74</v>
+      </c>
+      <c r="Q24" s="16">
         <v>10.8</v>
       </c>
-      <c r="Q24" s="14">
-        <v>0</v>
-      </c>
-      <c r="R24" s="16">
+      <c r="R24" s="14">
+        <v>5.55</v>
+      </c>
+      <c r="S24" s="16">
         <v>5.35</v>
       </c>
-      <c r="S24" s="14">
-        <v>0</v>
-      </c>
-      <c r="T24" s="16">
+      <c r="T24" s="14">
+        <v>11.2</v>
+      </c>
+      <c r="U24" s="16">
         <v>19.3</v>
       </c>
-      <c r="U24" s="14">
-        <v>0</v>
-      </c>
-      <c r="V24" s="16">
+      <c r="V24" s="14">
+        <v>3.11</v>
+      </c>
+      <c r="W24" s="16">
         <v>4.91</v>
       </c>
-      <c r="W24" s="14">
-        <v>0</v>
+      <c r="X24" s="14">
+        <v>12.2</v>
       </c>
     </row>
-    <row r="25" spans="1:23" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="33">
         <v>2002</v>
       </c>
       <c r="B25" s="34"/>
       <c r="C25" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D25" s="10">
         <v>0</v>
@@ -3014,46 +3088,49 @@
         <v>0</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L25" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M25" s="11">
         <v>2003</v>
       </c>
       <c r="N25" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="O25" s="10">
-        <v>0</v>
-      </c>
-      <c r="P25" s="12">
+        <v>28</v>
+      </c>
+      <c r="O25" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P25" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="12">
         <v>13.3</v>
       </c>
-      <c r="Q25" s="10">
-        <v>0</v>
-      </c>
-      <c r="R25" s="12">
+      <c r="R25" s="10">
+        <v>0</v>
+      </c>
+      <c r="S25" s="12">
         <v>16.5</v>
       </c>
-      <c r="S25" s="10">
-        <v>0</v>
-      </c>
-      <c r="T25" s="12">
+      <c r="T25" s="10">
+        <v>0</v>
+      </c>
+      <c r="U25" s="12">
         <v>24.4</v>
       </c>
-      <c r="U25" s="10">
-        <v>0</v>
-      </c>
-      <c r="V25" s="12">
+      <c r="V25" s="10">
+        <v>0</v>
+      </c>
+      <c r="W25" s="12">
         <v>5.9</v>
       </c>
-      <c r="W25" s="10">
+      <c r="X25" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:23" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="35">
         <v>2001</v>
       </c>
@@ -3083,46 +3160,49 @@
         <v>0.5</v>
       </c>
       <c r="K26" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L26" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M26" s="15">
         <v>2002</v>
       </c>
       <c r="N26" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="O26" s="14">
-        <v>0</v>
-      </c>
-      <c r="P26" s="16">
+        <v>28</v>
+      </c>
+      <c r="O26" s="16">
+        <v>12.16</v>
+      </c>
+      <c r="P26" s="14">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="Q26" s="16">
         <v>12.2</v>
       </c>
-      <c r="Q26" s="14">
-        <v>0</v>
-      </c>
-      <c r="R26" s="16">
+      <c r="R26" s="14">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="S26" s="16">
         <v>7.75</v>
       </c>
-      <c r="S26" s="14">
-        <v>0</v>
-      </c>
-      <c r="T26" s="16">
+      <c r="T26" s="14">
+        <v>6.45</v>
+      </c>
+      <c r="U26" s="16">
         <v>20.9</v>
       </c>
-      <c r="U26" s="14">
-        <v>0</v>
-      </c>
-      <c r="V26" s="16">
+      <c r="V26" s="14">
+        <v>2.39</v>
+      </c>
+      <c r="W26" s="16">
         <v>7.4</v>
       </c>
-      <c r="W26" s="14">
-        <v>0</v>
+      <c r="X26" s="14">
+        <v>6.76</v>
       </c>
     </row>
-    <row r="27" spans="1:23" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="33">
         <v>2000</v>
       </c>
@@ -3152,46 +3232,49 @@
         <v>1</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L27" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M27" s="11">
         <v>2001</v>
       </c>
       <c r="N27" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="O27" s="10">
-        <v>0</v>
-      </c>
-      <c r="P27" s="12">
+        <v>28</v>
+      </c>
+      <c r="O27" s="12">
+        <v>15.68</v>
+      </c>
+      <c r="P27" s="10">
+        <v>6.38</v>
+      </c>
+      <c r="Q27" s="12">
         <v>15.7</v>
       </c>
-      <c r="Q27" s="10">
-        <v>0</v>
-      </c>
-      <c r="R27" s="12">
+      <c r="R27" s="10">
+        <v>6.38</v>
+      </c>
+      <c r="S27" s="12">
         <v>11.8</v>
       </c>
-      <c r="S27" s="10">
-        <v>0</v>
-      </c>
-      <c r="T27" s="12">
+      <c r="T27" s="10">
+        <v>8.4700000000000006</v>
+      </c>
+      <c r="U27" s="12">
         <v>26.7</v>
       </c>
-      <c r="U27" s="10">
-        <v>0</v>
-      </c>
-      <c r="V27" s="12">
+      <c r="V27" s="10">
+        <v>3.75</v>
+      </c>
+      <c r="W27" s="12">
         <v>7.6</v>
       </c>
-      <c r="W27" s="10">
-        <v>0</v>
+      <c r="X27" s="10">
+        <v>13.2</v>
       </c>
     </row>
-    <row r="28" spans="1:23" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="35">
         <v>1999</v>
       </c>
@@ -3221,46 +3304,49 @@
         <v>5</v>
       </c>
       <c r="K28" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L28" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M28" s="15">
         <v>2000</v>
       </c>
       <c r="N28" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="O28" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="P28" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q28" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="R28" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="S28" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="T28" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="U28" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="V28" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="W28" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="O28" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="P28" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q28" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="R28" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="S28" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="T28" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="U28" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="V28" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="W28" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="X28" s="14" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:23" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="33">
         <v>1998</v>
       </c>
@@ -3290,52 +3376,55 @@
         <v>3.5</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L29" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M29" s="11">
         <v>1999</v>
       </c>
       <c r="N29" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="O29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="P29" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="R29" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="S29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="T29" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="U29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="V29" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="W29" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="O29" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P29" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q29" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="R29" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="S29" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="T29" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="U29" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="V29" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="W29" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="X29" s="10" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:23" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="35">
         <v>1997</v>
       </c>
       <c r="B30" s="36"/>
       <c r="C30" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D30" s="14">
         <v>0</v>
@@ -3359,52 +3448,55 @@
         <v>0</v>
       </c>
       <c r="K30" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L30" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M30" s="15">
         <v>1998</v>
       </c>
       <c r="N30" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="O30" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="P30" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q30" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="R30" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="S30" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="T30" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="U30" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="V30" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="W30" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="O30" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="P30" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q30" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="R30" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="S30" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="T30" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="U30" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="V30" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="W30" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="X30" s="14" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:23" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="33">
         <v>1996</v>
       </c>
       <c r="B31" s="34"/>
       <c r="C31" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D31" s="10">
         <v>0</v>
@@ -3428,48 +3520,51 @@
         <v>0</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L31" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M31" s="11">
         <v>1997</v>
       </c>
       <c r="N31" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="O31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="P31" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="R31" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="S31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="T31" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="U31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="V31" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="W31" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="O31" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P31" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q31" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="R31" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="S31" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="T31" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="U31" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="V31" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="W31" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="X31" s="10" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:23" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="35" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B32" s="36"/>
       <c r="C32" s="14"/>
@@ -3507,6 +3602,7 @@
       <c r="U32" s="14"/>
       <c r="V32" s="14"/>
       <c r="W32" s="14"/>
+      <c r="X32" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="42">
@@ -3536,10 +3632,10 @@
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="W3:X3"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A1:B1"/>
@@ -3547,13 +3643,14 @@
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="D1:L1"/>
-    <mergeCell ref="M1:W2"/>
+    <mergeCell ref="M1:X2"/>
     <mergeCell ref="D2:J2"/>
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="G3:I3"/>
-    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="N3:P3"/>
   </mergeCells>
   <phoneticPr fontId="22" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2443-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2443-dividend-20260215_1_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{73F2286D-D786-45C3-8AD5-9A2937EFBF5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C31678AD-016F-45A3-B6B1-BA0DA008E514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" xr2:uid="{1610C540-A757-47F3-91C8-C0BD0FE44C13}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{68CE72BD-349E-4B8D-928D-EF0DBFF7E3E3}"/>
   </bookViews>
   <sheets>
     <sheet name="2443-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1412,20 +1412,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DD08B43-C646-49B2-B747-D7909BAE4B17}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{586B0D1C-D97C-4358-B829-6CC43BB60A08}">
   <dimension ref="A1:X32"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="12.6640625" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="14" width="7.88671875" customWidth="1"/>
-    <col min="15" max="15" width="8.21875" customWidth="1"/>
-    <col min="16" max="18" width="7.88671875" customWidth="1"/>
-    <col min="19" max="19" width="8.21875" customWidth="1"/>
-    <col min="20" max="20" width="7.88671875" customWidth="1"/>
-    <col min="21" max="21" width="8.21875" customWidth="1"/>
-    <col min="22" max="23" width="7.88671875" customWidth="1"/>
-    <col min="24" max="24" width="9.33203125" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="14" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
@@ -3651,6 +3649,5 @@
   </mergeCells>
   <phoneticPr fontId="22" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>